--- a/SGC-CKN/Excel/d50a318c-935e-466b-ba5c-c7e9854a922c_Lô_CT-02_P11-8_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/d50a318c-935e-466b-ba5c-c7e9854a922c_Lô_CT-02_P11-8_D800_25-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -102,7 +102,7 @@
 25/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">14:06
+    <t xml:space="preserve">14:00
 25/03/2026</t>
   </si>
   <si>
@@ -123,10 +123,6 @@
   </si>
   <si>
     <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:22
-25/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:35
@@ -339,12 +335,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -500,17 +496,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1149,19 +1145,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.68</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-3.28</v>
+        <v>-1.6</v>
       </c>
       <c r="H11" s="5">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="I11" s="5">
         <v>1.6</v>
       </c>
       <c r="J11" s="8">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1184,89 +1180,89 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
+        <v>-1.6</v>
+      </c>
+      <c r="G12" s="9">
         <v>-3.28</v>
       </c>
-      <c r="G12" s="9">
-        <v>-13.48</v>
-      </c>
       <c r="H12" s="9">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="I12" s="9">
-        <v>10.2</v>
-      </c>
-      <c r="J12" s="12">
-        <v>8.27</v>
+        <v>1.68</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1.26</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
+        <v>-3.28</v>
+      </c>
+      <c r="G13" s="12">
         <v>-13.48</v>
       </c>
-      <c r="G13" s="13">
-        <v>-18.68</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0.22</v>
-      </c>
-      <c r="I13" s="13">
-        <v>5.2</v>
-      </c>
-      <c r="J13" s="12">
-        <v>24</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="H13" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="12">
+        <v>10.2</v>
+      </c>
+      <c r="J13" s="15">
+        <v>40.8</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="16">
+        <v>-13.48</v>
+      </c>
+      <c r="G14" s="16">
         <v>-18.68</v>
-      </c>
-      <c r="G14" s="16">
-        <v>-30.7</v>
       </c>
       <c r="H14" s="16">
         <v>0.92</v>
       </c>
       <c r="I14" s="16">
-        <v>12.02</v>
-      </c>
-      <c r="J14" s="12">
-        <v>13.11</v>
+        <v>5.2</v>
+      </c>
+      <c r="J14" s="15">
+        <v>5.67</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1274,34 +1270,34 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>43</v>
-      </c>
       <c r="F15" s="19">
+        <v>-18.68</v>
+      </c>
+      <c r="G15" s="19">
         <v>-30.7</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-36.18</v>
       </c>
       <c r="H15" s="19">
         <v>0.5</v>
       </c>
       <c r="I15" s="19">
-        <v>5.48</v>
-      </c>
-      <c r="J15" s="12">
-        <v>10.96</v>
+        <v>12.02</v>
+      </c>
+      <c r="J15" s="15">
+        <v>24.04</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1309,34 +1305,34 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>46</v>
-      </c>
       <c r="F16" s="22">
+        <v>-30.7</v>
+      </c>
+      <c r="G16" s="22">
         <v>-36.18</v>
-      </c>
-      <c r="G16" s="22">
-        <v>-38.68</v>
       </c>
       <c r="H16" s="22">
         <v>1.5</v>
       </c>
       <c r="I16" s="22">
-        <v>2.5</v>
+        <v>5.48</v>
       </c>
       <c r="J16" s="8">
-        <v>1.67</v>
+        <v>3.65</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1344,22 +1340,22 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>49</v>
-      </c>
       <c r="F17" s="25">
-        <v>-38.68</v>
+        <v>-36.18</v>
       </c>
       <c r="G17" s="25">
         <v>-44.68</v>
@@ -1368,10 +1364,10 @@
         <v>2.33</v>
       </c>
       <c r="I17" s="25">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="J17" s="8">
-        <v>2.57</v>
+        <v>3.64</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1379,19 +1375,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-44.68</v>
@@ -1414,7 +1410,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1520,31 +1516,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1561,19 +1557,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.68</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-3.28</v>
+        <v>-1.6</v>
       </c>
       <c r="G2" s="5">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H2" s="5">
         <v>1.6</v>
       </c>
       <c r="I2" s="8">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1590,48 +1586,48 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
+        <v>-1.6</v>
+      </c>
+      <c r="F3" s="9">
         <v>-3.28</v>
       </c>
-      <c r="F3" s="9">
+      <c r="G3" s="9">
+        <v>1.33</v>
+      </c>
+      <c r="H3" s="9">
+        <v>1.68</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12">
+        <v>-3.28</v>
+      </c>
+      <c r="F4" s="12">
         <v>-13.48</v>
       </c>
-      <c r="G3" s="9">
-        <v>1.23</v>
-      </c>
-      <c r="H3" s="9">
+      <c r="G4" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="12">
         <v>10.2</v>
       </c>
-      <c r="I3" s="12">
-        <v>8.27</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="13">
-        <v>1</v>
-      </c>
-      <c r="E4" s="13">
-        <v>-13.48</v>
-      </c>
-      <c r="F4" s="13">
-        <v>-18.68</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0.22</v>
-      </c>
-      <c r="H4" s="13">
-        <v>5.2</v>
-      </c>
-      <c r="I4" s="12">
-        <v>24</v>
+      <c r="I4" s="15">
+        <v>40.8</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1642,25 +1638,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
       </c>
       <c r="E5" s="16">
+        <v>-13.48</v>
+      </c>
+      <c r="F5" s="16">
         <v>-18.68</v>
-      </c>
-      <c r="F5" s="16">
-        <v>-30.7</v>
       </c>
       <c r="G5" s="16">
         <v>0.92</v>
       </c>
       <c r="H5" s="16">
-        <v>12.02</v>
-      </c>
-      <c r="I5" s="12">
-        <v>13.11</v>
+        <v>5.2</v>
+      </c>
+      <c r="I5" s="15">
+        <v>5.67</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1671,25 +1667,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
       <c r="E6" s="19">
+        <v>-18.68</v>
+      </c>
+      <c r="F6" s="19">
         <v>-30.7</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-36.18</v>
       </c>
       <c r="G6" s="19">
         <v>0.5</v>
       </c>
       <c r="H6" s="19">
-        <v>5.48</v>
-      </c>
-      <c r="I6" s="12">
-        <v>10.96</v>
+        <v>12.02</v>
+      </c>
+      <c r="I6" s="15">
+        <v>24.04</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1700,25 +1696,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
+        <v>-30.7</v>
+      </c>
+      <c r="F7" s="22">
         <v>-36.18</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-38.68</v>
       </c>
       <c r="G7" s="22">
         <v>1.5</v>
       </c>
       <c r="H7" s="22">
-        <v>2.5</v>
+        <v>5.48</v>
       </c>
       <c r="I7" s="8">
-        <v>1.67</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1729,13 +1725,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-38.68</v>
+        <v>-36.18</v>
       </c>
       <c r="F8" s="25">
         <v>-44.68</v>
@@ -1744,10 +1740,10 @@
         <v>2.33</v>
       </c>
       <c r="H8" s="25">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I8" s="8">
-        <v>2.57</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1758,7 +1754,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1781,7 +1777,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1793,19 +1789,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-1.68</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-50.15</v>
       </c>
       <c r="G10" s="33">
-        <v>8.72</v>
+        <v>8.75</v>
       </c>
       <c r="H10" s="33">
-        <v>48.47</v>
+        <v>50.15</v>
       </c>
       <c r="I10" s="33">
-        <v>5.56</v>
+        <v>5.73</v>
       </c>
     </row>
   </sheetData>
